--- a/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_J_Monthly_Performance_Report.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_J_Monthly_Performance_Report.xlsx
@@ -616,6 +616,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -678,6 +686,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>

--- a/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_J_Monthly_Performance_Report.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_J_Monthly_Performance_Report.xlsx
@@ -619,7 +619,7 @@
     <row r="3">
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
         </is>
       </c>
     </row>
